--- a/AtchisonRegime/Outputs/Brazil/df_regCLI_Brazil.xlsx
+++ b/AtchisonRegime/Outputs/Brazil/df_regCLI_Brazil.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H401"/>
+  <dimension ref="A1:H402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10595,22 +10595,22 @@
         <v>45443</v>
       </c>
       <c r="B391" t="n">
-        <v>102.02</v>
+        <v>102.0425</v>
       </c>
       <c r="C391" t="n">
-        <v>101.9166666666667</v>
+        <v>101.9241666666667</v>
       </c>
       <c r="D391" t="n">
-        <v>100.815</v>
+        <v>100.815625</v>
       </c>
       <c r="E391" t="n">
-        <v>1.426475176290024</v>
+        <v>1.427023047040916</v>
       </c>
       <c r="F391" t="b">
         <v>1</v>
       </c>
       <c r="G391" t="n">
-        <v>0.07010286730686353</v>
+        <v>0.08584304244701514</v>
       </c>
       <c r="H391" t="b">
         <v>1</v>
@@ -10621,22 +10621,22 @@
         <v>45473</v>
       </c>
       <c r="B392" t="n">
-        <v>102.11</v>
+        <v>102.1417</v>
       </c>
       <c r="C392" t="n">
-        <v>102.0166666666667</v>
+        <v>102.0347333333333</v>
       </c>
       <c r="D392" t="n">
-        <v>100.7586111111111</v>
+        <v>100.7601166666667</v>
       </c>
       <c r="E392" t="n">
-        <v>1.32800635277701</v>
+        <v>1.329553100535319</v>
       </c>
       <c r="F392" t="b">
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0.06777076014117203</v>
+        <v>0.07461153673370037</v>
       </c>
       <c r="H392" t="b">
         <v>1</v>
@@ -10647,22 +10647,22 @@
         <v>45504</v>
       </c>
       <c r="B393" t="n">
-        <v>102.21</v>
+        <v>102.2348</v>
       </c>
       <c r="C393" t="n">
-        <v>102.1133333333333</v>
+        <v>102.1396666666667</v>
       </c>
       <c r="D393" t="n">
-        <v>100.7088888888889</v>
+        <v>100.7110833333333</v>
       </c>
       <c r="E393" t="n">
-        <v>1.23331093930772</v>
+        <v>1.235905612785421</v>
       </c>
       <c r="F393" t="b">
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.08108255332278663</v>
+        <v>0.07532937712790448</v>
       </c>
       <c r="H393" t="b">
         <v>1</v>
@@ -10673,22 +10673,22 @@
         <v>45535</v>
       </c>
       <c r="B394" t="n">
-        <v>102.25</v>
+        <v>102.2807</v>
       </c>
       <c r="C394" t="n">
-        <v>102.19</v>
+        <v>102.2190666666667</v>
       </c>
       <c r="D394" t="n">
-        <v>100.6691666666667</v>
+        <v>100.6722138888889</v>
       </c>
       <c r="E394" t="n">
-        <v>1.15545507423337</v>
+        <v>1.159507706166262</v>
       </c>
       <c r="F394" t="b">
         <v>1</v>
       </c>
       <c r="G394" t="n">
-        <v>0.03461839485758089</v>
+        <v>0.03958576536912412</v>
       </c>
       <c r="H394" t="b">
         <v>1</v>
@@ -10699,22 +10699,22 @@
         <v>45565</v>
       </c>
       <c r="B395" t="n">
-        <v>102.21</v>
+        <v>102.2421</v>
       </c>
       <c r="C395" t="n">
-        <v>102.2233333333333</v>
+        <v>102.2525333333333</v>
       </c>
       <c r="D395" t="n">
-        <v>100.6416666666667</v>
+        <v>100.6456055555555</v>
       </c>
       <c r="E395" t="n">
-        <v>1.104141554072115</v>
+        <v>1.10976684654154</v>
       </c>
       <c r="F395" t="b">
         <v>0</v>
       </c>
       <c r="G395" t="n">
-        <v>-0.0362272390278989</v>
+        <v>-0.03478208068685314</v>
       </c>
       <c r="H395" t="b">
         <v>1</v>
@@ -10725,22 +10725,22 @@
         <v>45596</v>
       </c>
       <c r="B396" t="n">
-        <v>102.08</v>
+        <v>102.1153</v>
       </c>
       <c r="C396" t="n">
-        <v>102.18</v>
+        <v>102.2127</v>
       </c>
       <c r="D396" t="n">
-        <v>100.6263888888889</v>
+        <v>100.6313083333333</v>
       </c>
       <c r="E396" t="n">
-        <v>1.079370591139154</v>
+        <v>1.086543767411241</v>
       </c>
       <c r="F396" t="b">
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>-0.1204405614412703</v>
+        <v>-0.1167003150752939</v>
       </c>
       <c r="H396" t="b">
         <v>1</v>
@@ -10751,22 +10751,22 @@
         <v>45626</v>
       </c>
       <c r="B397" t="n">
-        <v>101.9</v>
+        <v>101.9296</v>
       </c>
       <c r="C397" t="n">
-        <v>102.0633333333333</v>
+        <v>102.0956666666667</v>
       </c>
       <c r="D397" t="n">
-        <v>100.6222222222222</v>
+        <v>100.6279638888889</v>
       </c>
       <c r="E397" t="n">
-        <v>1.073994176922625</v>
+        <v>1.082228917995014</v>
       </c>
       <c r="F397" t="b">
         <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>-0.1675986740596273</v>
+        <v>-0.1715903141306255</v>
       </c>
       <c r="H397" t="b">
         <v>0</v>
@@ -10777,22 +10777,22 @@
         <v>45657</v>
       </c>
       <c r="B398" t="n">
-        <v>101.71</v>
+        <v>101.7307</v>
       </c>
       <c r="C398" t="n">
-        <v>101.8966666666667</v>
+        <v>101.9252</v>
       </c>
       <c r="D398" t="n">
-        <v>100.6277777777778</v>
+        <v>100.6340944444444</v>
       </c>
       <c r="E398" t="n">
-        <v>1.079222236113048</v>
+        <v>1.087978023660619</v>
       </c>
       <c r="F398" t="b">
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>-0.1760527105930659</v>
+        <v>-0.1828161926752659</v>
       </c>
       <c r="H398" t="b">
         <v>0</v>
@@ -10803,22 +10803,22 @@
         <v>45688</v>
       </c>
       <c r="B399" t="n">
-        <v>101.55</v>
+        <v>101.5589</v>
       </c>
       <c r="C399" t="n">
-        <v>101.72</v>
+        <v>101.7397333333333</v>
       </c>
       <c r="D399" t="n">
-        <v>100.6413888888889</v>
+        <v>100.6479527777778</v>
       </c>
       <c r="E399" t="n">
-        <v>1.087884323624307</v>
+        <v>1.096700534066091</v>
       </c>
       <c r="F399" t="b">
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>-0.1470744605152078</v>
+        <v>-0.1566516972167822</v>
       </c>
       <c r="H399" t="b">
         <v>0</v>
@@ -10829,22 +10829,22 @@
         <v>45716</v>
       </c>
       <c r="B400" t="n">
-        <v>101.46</v>
+        <v>101.4541</v>
       </c>
       <c r="C400" t="n">
-        <v>101.5733333333333</v>
+        <v>101.5812333333333</v>
       </c>
       <c r="D400" t="n">
-        <v>100.6613888888889</v>
+        <v>100.6677888888889</v>
       </c>
       <c r="E400" t="n">
-        <v>1.096334549507886</v>
+        <v>1.104840749165275</v>
       </c>
       <c r="F400" t="b">
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>-0.08209173015700538</v>
+        <v>-0.09485529935348186</v>
       </c>
       <c r="H400" t="b">
         <v>0</v>
@@ -10855,24 +10855,50 @@
         <v>45747</v>
       </c>
       <c r="B401" t="n">
-        <v>101.43</v>
+        <v>101.4032</v>
       </c>
       <c r="C401" t="n">
-        <v>101.48</v>
+        <v>101.4720666666667</v>
       </c>
       <c r="D401" t="n">
-        <v>100.6869444444444</v>
+        <v>100.6926</v>
       </c>
       <c r="E401" t="n">
-        <v>1.103404651701742</v>
+        <v>1.111206920682032</v>
       </c>
       <c r="F401" t="b">
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>-0.02718857488385517</v>
+        <v>-0.04580605020778437</v>
       </c>
       <c r="H401" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B402" t="n">
+        <v>101.379</v>
+      </c>
+      <c r="C402" t="n">
+        <v>101.4121</v>
+      </c>
+      <c r="D402" t="n">
+        <v>100.7214611111111</v>
+      </c>
+      <c r="E402" t="n">
+        <v>1.115272679348778</v>
+      </c>
+      <c r="F402" t="b">
+        <v>0</v>
+      </c>
+      <c r="G402" t="n">
+        <v>-0.02169872933148871</v>
+      </c>
+      <c r="H402" t="b">
         <v>0</v>
       </c>
     </row>
